--- a/livrables/km_a_doubler.xlsx
+++ b/livrables/km_a_doubler.xlsx
@@ -439,7 +439,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
         <v>206.03</v>
       </c>
       <c r="F2" t="n">
-        <v>183.28</v>
+        <v>184.31</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         <v>123.21</v>
       </c>
       <c r="F3" t="n">
-        <v>113.82</v>
+        <v>114.22</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>109.31</v>
       </c>
       <c r="F4" t="n">
-        <v>103.12</v>
+        <v>103.49</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -627,19 +627,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="C5" t="n">
         <v>9.19</v>
       </c>
       <c r="D5" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="F5" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>1.97</v>
       </c>
       <c r="C6" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="D6" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="E6" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="F6" t="n">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Québec</t>
+          <t>Saint-Lambert</t>
         </is>
       </c>
     </row>
@@ -711,13 +711,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="C7" t="n">
         <v>9.19</v>
       </c>
       <c r="D7" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
